--- a/Tests/Validation/Stock/Thomas2007Observed.xlsx
+++ b/Tests/Validation/Stock/Thomas2007Observed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Repos\ApsimX\Tests\Validation\Stock\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEO027\ApsimX\Tests\Validation\Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13D98B1-C059-4B6D-BDA9-B43445D8E04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AEEDC5-9B58-4D4F-9F62-75A2C35446F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ValidationData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="24">
   <si>
     <t>SimulationName</t>
   </si>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>OMD76</t>
+  </si>
+  <si>
+    <t>Stock.CFleeceWtAll</t>
+  </si>
+  <si>
+    <t>Stock.CFleeceGrowthAll</t>
   </si>
 </sst>
 </file>
@@ -446,21 +452,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1048564"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K1048564"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,8 +494,14 @@
       <c r="I1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f t="shared" ref="A2:A33" si="0">"Thomas2007"&amp;C2</f>
         <v>Thomas2007OMD55</v>
@@ -506,7 +518,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -524,7 +536,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -542,7 +554,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -560,7 +572,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -584,7 +596,7 @@
         <v>1.7010000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -606,7 +618,7 @@
         <v>3.3620000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -628,7 +640,7 @@
         <v>5.1150000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -650,7 +662,7 @@
         <v>6.7700000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -672,7 +684,7 @@
         <v>8.4740000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -694,7 +706,7 @@
         <v>10.003</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -716,7 +728,7 @@
         <v>11.731999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -739,8 +751,12 @@
         <f t="shared" si="2"/>
         <v>13.447999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I13">
+        <f>(G13-G6)</f>
+        <v>1.2999999999999972</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -762,7 +778,7 @@
         <v>14.996999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -784,7 +800,7 @@
         <v>16.843999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -806,7 +822,7 @@
         <v>18.415999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -828,7 +844,7 @@
         <v>19.786999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -850,7 +866,7 @@
         <v>21.317999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -872,7 +888,7 @@
         <v>22.856999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -895,8 +911,15 @@
         <f t="shared" si="2"/>
         <v>24.999999999999996</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20">
+        <f>(G20-G13)+I13</f>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="J20">
+        <v>0.69968785791308608</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -918,7 +941,7 @@
         <v>26.737999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -940,7 +963,7 @@
         <v>28.357999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -962,7 +985,7 @@
         <v>30.159999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -984,7 +1007,7 @@
         <v>31.869999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1006,7 +1029,7 @@
         <v>33.461999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1028,7 +1051,7 @@
         <v>34.858999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1051,8 +1074,12 @@
         <f t="shared" si="2"/>
         <v>36.191999999999993</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27">
+        <f>(G27-G20)+I20</f>
+        <v>1.8999999999999986</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1074,7 +1101,7 @@
         <v>37.620999999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1096,7 +1123,7 @@
         <v>39.280999999999992</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1118,7 +1145,7 @@
         <v>40.699999999999989</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1140,7 +1167,7 @@
         <v>42.370999999999988</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1162,7 +1189,7 @@
         <v>44.023999999999987</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>Thomas2007OMD55</v>
@@ -1184,7 +1211,7 @@
         <v>45.734999999999985</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" ref="A34:A65" si="3">"Thomas2007"&amp;C34</f>
         <v>Thomas2007OMD55</v>
@@ -1207,8 +1234,12 @@
         <f t="shared" si="2"/>
         <v>47.414999999999985</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I34">
+        <f>(G34-G27)+I27</f>
+        <v>1.6999999999999957</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1230,7 +1261,7 @@
         <v>49.031999999999982</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1252,7 +1283,7 @@
         <v>50.547999999999981</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1274,7 +1305,7 @@
         <v>52.21899999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1296,7 +1327,7 @@
         <v>53.830999999999982</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1318,7 +1349,7 @@
         <v>55.362999999999985</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1340,7 +1371,7 @@
         <v>57.091999999999985</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1363,9 +1394,18 @@
         <f t="shared" si="2"/>
         <v>58.247999999999983</v>
       </c>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I41">
+        <f>(G41-G34)+I34</f>
+        <v>2.1000000000000014</v>
+      </c>
+      <c r="J41">
+        <v>0.9978542663362342</v>
+      </c>
+      <c r="K41">
+        <v>1.4198400401102292E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1388,7 +1428,7 @@
       </c>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1411,7 +1451,7 @@
       </c>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1434,7 +1474,7 @@
       </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1457,7 +1497,7 @@
       </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1480,7 +1520,7 @@
       </c>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1503,7 +1543,7 @@
       </c>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD55</v>
@@ -1526,9 +1566,12 @@
         <f t="shared" si="2"/>
         <v>67.006999999999991</v>
       </c>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I48">
+        <f>(G48-G41)+I41</f>
+        <v>0.79999999999999716</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1545,7 +1588,7 @@
       </c>
       <c r="G49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1562,7 +1605,7 @@
       </c>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1579,7 +1622,7 @@
       </c>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1596,7 +1639,7 @@
       </c>
       <c r="G52" s="3"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1619,7 +1662,7 @@
         <v>1.8580000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1640,7 +1683,7 @@
         <v>3.6230000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1661,7 +1704,7 @@
         <v>5.5760000000000005</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1682,7 +1725,7 @@
         <v>7.4970000000000008</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1703,7 +1746,7 @@
         <v>9.2580000000000009</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1724,7 +1767,7 @@
         <v>11.152000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1745,7 +1788,7 @@
         <v>13.008000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1767,8 +1810,12 @@
         <f t="shared" si="4"/>
         <v>14.727</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I60">
+        <f>(G60-G53)</f>
+        <v>0.80000000000000426</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1789,7 +1836,7 @@
         <v>16.615000000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1810,7 +1857,7 @@
         <v>18.522000000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1831,7 +1878,7 @@
         <v>20.412000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1852,7 +1899,7 @@
         <v>21.922000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f t="shared" si="3"/>
         <v>Thomas2007OMD62</v>
@@ -1873,7 +1920,7 @@
         <v>23.846000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f t="shared" ref="A66:A97" si="6">"Thomas2007"&amp;C66</f>
         <v>Thomas2007OMD62</v>
@@ -1894,7 +1941,7 @@
         <v>25.546000000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -1916,8 +1963,15 @@
         <f t="shared" si="4"/>
         <v>27.470000000000002</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I67">
+        <f>(G67-G60)+I60</f>
+        <v>1.5</v>
+      </c>
+      <c r="J67">
+        <v>0.53480966591716261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -1938,7 +1992,7 @@
         <v>29.201000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -1959,7 +2013,7 @@
         <v>31.190000000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -1980,7 +2034,7 @@
         <v>33.086000000000006</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2001,7 +2055,7 @@
         <v>34.831000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2022,7 +2076,7 @@
         <v>36.690000000000005</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2043,7 +2097,7 @@
         <v>38.639000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2065,8 +2119,12 @@
         <f t="shared" si="4"/>
         <v>40.504000000000005</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I74">
+        <f>(G74-G67)+I67</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2087,7 +2145,7 @@
         <v>42.424000000000007</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2108,7 +2166,7 @@
         <v>44.27000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2129,7 +2187,7 @@
         <v>46.060000000000009</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2150,7 +2208,7 @@
         <v>47.808000000000007</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2171,7 +2229,7 @@
         <v>49.615000000000009</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2192,7 +2250,7 @@
         <v>51.484000000000009</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2214,8 +2272,12 @@
         <f t="shared" si="4"/>
         <v>53.180000000000007</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I81">
+        <f>(G81-G74)+I74</f>
+        <v>3.2000000000000028</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2236,7 +2298,7 @@
         <v>55.225000000000009</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2257,7 +2319,7 @@
         <v>57.01100000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2278,7 +2340,7 @@
         <v>58.876000000000012</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2299,7 +2361,7 @@
         <v>60.646000000000015</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2320,7 +2382,7 @@
         <v>62.418000000000013</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2341,7 +2403,7 @@
         <v>64.198000000000008</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2363,8 +2425,18 @@
         <f t="shared" si="4"/>
         <v>65.494000000000014</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I88">
+        <f>(G88-G81)+I81</f>
+        <v>4.3000000000000043</v>
+      </c>
+      <c r="J88">
+        <v>0.83420084909792858</v>
+      </c>
+      <c r="K88">
+        <v>1.4256723008607903E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2384,8 +2456,9 @@
         <f t="shared" si="4"/>
         <v>66.864000000000019</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I89" s="2"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2405,8 +2478,9 @@
         <f t="shared" si="4"/>
         <v>67.793000000000021</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I90" s="2"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2426,8 +2500,9 @@
         <f t="shared" si="4"/>
         <v>68.871000000000024</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2447,8 +2522,9 @@
         <f t="shared" si="4"/>
         <v>70.183000000000021</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I92" s="2"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2468,8 +2544,9 @@
         <f t="shared" si="4"/>
         <v>71.424000000000021</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2489,8 +2566,9 @@
         <f t="shared" si="4"/>
         <v>72.673000000000016</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD62</v>
@@ -2512,8 +2590,12 @@
         <f t="shared" si="4"/>
         <v>73.836000000000013</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I95">
+        <f>(G95-G88)+I88</f>
+        <v>-1.0999999999999943</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD69</v>
@@ -2529,7 +2611,7 @@
       </c>
       <c r="G96" s="4"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f t="shared" si="6"/>
         <v>Thomas2007OMD69</v>
@@ -2546,7 +2628,7 @@
       </c>
       <c r="G97" s="3"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="str">
         <f t="shared" ref="A98:A129" si="7">"Thomas2007"&amp;C98</f>
         <v>Thomas2007OMD69</v>
@@ -2563,7 +2645,7 @@
       </c>
       <c r="G98" s="3"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2580,7 +2662,7 @@
       </c>
       <c r="G99" s="3"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2603,7 +2685,7 @@
         <v>1.9810000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2624,7 +2706,7 @@
         <v>3.835</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2645,7 +2727,7 @@
         <v>5.4450000000000003</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2666,7 +2748,7 @@
         <v>7.3559999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2687,7 +2769,7 @@
         <v>9.0960000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2708,7 +2790,7 @@
         <v>10.975999999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2729,7 +2811,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2751,8 +2833,12 @@
         <f t="shared" si="8"/>
         <v>14.859</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I107">
+        <f>(G107-G100)</f>
+        <v>0.79999999999999716</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2773,7 +2859,7 @@
         <v>16.728999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2794,7 +2880,7 @@
         <v>18.587</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2815,7 +2901,7 @@
         <v>20.402000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2836,7 +2922,7 @@
         <v>22.01</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2857,7 +2943,7 @@
         <v>23.807000000000002</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2878,7 +2964,7 @@
         <v>25.348000000000003</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2900,8 +2986,15 @@
         <f t="shared" si="8"/>
         <v>26.927000000000003</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I114">
+        <f>(G114-G107)+I107</f>
+        <v>1.1999999999999957</v>
+      </c>
+      <c r="J114">
+        <v>0.67399306346768062</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2922,7 +3015,7 @@
         <v>28.460000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2943,7 +3036,7 @@
         <v>29.873000000000005</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2964,7 +3057,7 @@
         <v>31.358000000000004</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -2985,7 +3078,7 @@
         <v>32.867000000000004</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3006,7 +3099,7 @@
         <v>34.407000000000004</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3027,7 +3120,7 @@
         <v>36.185000000000002</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3049,8 +3142,12 @@
         <f t="shared" si="8"/>
         <v>37.836000000000006</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I121">
+        <f>(G121-G114)+I114</f>
+        <v>1.7999999999999972</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3071,7 +3168,7 @@
         <v>39.587000000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3092,7 +3189,7 @@
         <v>41.578000000000003</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3113,7 +3210,7 @@
         <v>43.268000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3134,7 +3231,7 @@
         <v>45.395000000000003</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3155,7 +3252,7 @@
         <v>47.103000000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3176,7 +3273,7 @@
         <v>48.753</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3198,8 +3295,12 @@
         <f t="shared" si="8"/>
         <v>50.494</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I128">
+        <f>(G128-G121)+I121</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="str">
         <f t="shared" si="7"/>
         <v>Thomas2007OMD69</v>
@@ -3220,7 +3321,7 @@
         <v>52.392000000000003</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="str">
         <f t="shared" ref="A130:A161" si="10">"Thomas2007"&amp;C130</f>
         <v>Thomas2007OMD69</v>
@@ -3241,7 +3342,7 @@
         <v>54.086000000000006</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3262,7 +3363,7 @@
         <v>55.818000000000005</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3283,7 +3384,7 @@
         <v>57.465000000000003</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3304,7 +3405,7 @@
         <v>59.209000000000003</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3325,7 +3426,7 @@
         <v>61.029000000000003</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3347,8 +3448,18 @@
         <f t="shared" si="8"/>
         <v>62.114000000000004</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I135">
+        <f>(G135-G128)+I128</f>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="J135">
+        <v>1.0328285506409614</v>
+      </c>
+      <c r="K135">
+        <v>1.7087404151108605E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3368,8 +3479,9 @@
         <f t="shared" si="8"/>
         <v>63.574000000000005</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I136" s="2"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3389,8 +3501,9 @@
         <f t="shared" si="8"/>
         <v>64.690000000000012</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I137" s="2"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3410,8 +3523,9 @@
         <f t="shared" si="8"/>
         <v>65.849000000000018</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I138" s="2"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3431,8 +3545,9 @@
         <f t="shared" si="8"/>
         <v>66.982000000000014</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I139" s="2"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3452,8 +3567,9 @@
         <f t="shared" si="8"/>
         <v>68.26700000000001</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I140" s="2"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3473,8 +3589,9 @@
         <f t="shared" si="8"/>
         <v>69.572000000000017</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I141" s="2"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD69</v>
@@ -3496,8 +3613,12 @@
         <f t="shared" si="8"/>
         <v>70.968000000000018</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I142">
+        <f>(G142-G135)+I135</f>
+        <v>2.2999999999999972</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3513,7 +3634,7 @@
       </c>
       <c r="G143" s="4"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3530,7 +3651,7 @@
       </c>
       <c r="G144" s="3"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3547,7 +3668,7 @@
       </c>
       <c r="G145" s="3"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3564,7 +3685,7 @@
       </c>
       <c r="G146" s="3"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3587,7 +3708,7 @@
         <v>1.9710000000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3608,7 +3729,7 @@
         <v>3.415</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3629,7 +3750,7 @@
         <v>5.2989999999999995</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3650,7 +3771,7 @@
         <v>7.1389999999999993</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3671,7 +3792,7 @@
         <v>9.01</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3692,7 +3813,7 @@
         <v>10.725999999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3713,7 +3834,7 @@
         <v>12.569999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3735,8 +3856,12 @@
         <f t="shared" si="11"/>
         <v>14.206999999999999</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I154">
+        <f>(G154-G147)</f>
+        <v>1.2000000000000028</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3757,7 +3882,7 @@
         <v>15.938999999999998</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3778,7 +3903,7 @@
         <v>17.680999999999997</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3799,7 +3924,7 @@
         <v>19.462999999999997</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3820,7 +3945,7 @@
         <v>20.680999999999997</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3841,7 +3966,7 @@
         <v>22.324999999999996</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3862,7 +3987,7 @@
         <v>23.977999999999994</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="str">
         <f t="shared" si="10"/>
         <v>Thomas2007OMD76</v>
@@ -3884,8 +4009,15 @@
         <f t="shared" si="11"/>
         <v>25.483999999999995</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I161">
+        <f>(G161-G154)+I154</f>
+        <v>1.5</v>
+      </c>
+      <c r="J161">
+        <v>0.63642254540008492</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="str">
         <f t="shared" ref="A162:A182" si="12">"Thomas2007"&amp;C162</f>
         <v>Thomas2007OMD76</v>
@@ -3906,7 +4038,7 @@
         <v>26.875999999999994</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -3927,7 +4059,7 @@
         <v>28.519999999999992</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -3948,7 +4080,7 @@
         <v>30.175999999999991</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -3969,7 +4101,7 @@
         <v>31.570999999999991</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -3990,7 +4122,7 @@
         <v>33.142999999999994</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4011,7 +4143,7 @@
         <v>34.849999999999994</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4033,8 +4165,12 @@
         <f t="shared" si="11"/>
         <v>36.425999999999995</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I168">
+        <f>(G168-G161)+I161</f>
+        <v>2.2000000000000028</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4055,7 +4191,7 @@
         <v>37.970999999999997</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4076,7 +4212,7 @@
         <v>39.464999999999996</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4097,7 +4233,7 @@
         <v>41.062999999999995</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4118,7 +4254,7 @@
         <v>42.670999999999992</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4139,7 +4275,7 @@
         <v>44.248999999999995</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4160,7 +4296,7 @@
         <v>45.839999999999996</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4182,8 +4318,12 @@
         <f t="shared" si="11"/>
         <v>47.326999999999998</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I175">
+        <f>(G175-G168)+I168</f>
+        <v>3.2999999999999972</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4204,7 +4344,7 @@
         <v>48.997999999999998</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4225,7 +4365,7 @@
         <v>50.769999999999996</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4246,7 +4386,7 @@
         <v>52.371999999999993</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4267,7 +4407,7 @@
         <v>54.019999999999996</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4288,7 +4428,7 @@
         <v>55.545999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4309,7 +4449,7 @@
         <v>57.247</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="str">
         <f t="shared" si="12"/>
         <v>Thomas2007OMD76</v>
@@ -4331,8 +4471,18 @@
         <f t="shared" si="11"/>
         <v>58.192</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I182">
+        <f>(G182-G175)+I175</f>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="J182">
+        <v>0.9644430836057849</v>
+      </c>
+      <c r="K182">
+        <v>1.5620025628842857E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="str">
         <f t="shared" ref="A183:A189" si="13">"Thomas2007"&amp;C183</f>
         <v>Thomas2007OMD76</v>
@@ -4352,8 +4502,9 @@
         <f t="shared" si="11"/>
         <v>59.49</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I183" s="2"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="str">
         <f t="shared" si="13"/>
         <v>Thomas2007OMD76</v>
@@ -4373,8 +4524,9 @@
         <f t="shared" si="11"/>
         <v>60.722000000000001</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I184" s="2"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="str">
         <f t="shared" si="13"/>
         <v>Thomas2007OMD76</v>
@@ -4394,8 +4546,9 @@
         <f t="shared" si="11"/>
         <v>62.097000000000001</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I185" s="2"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="str">
         <f t="shared" si="13"/>
         <v>Thomas2007OMD76</v>
@@ -4415,8 +4568,9 @@
         <f t="shared" si="11"/>
         <v>63.569000000000003</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I186" s="2"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="str">
         <f t="shared" si="13"/>
         <v>Thomas2007OMD76</v>
@@ -4436,8 +4590,9 @@
         <f t="shared" si="11"/>
         <v>64.948000000000008</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I187" s="2"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="str">
         <f t="shared" si="13"/>
         <v>Thomas2007OMD76</v>
@@ -4457,8 +4612,9 @@
         <f t="shared" si="11"/>
         <v>66.381000000000014</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I188" s="2"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="str">
         <f t="shared" si="13"/>
         <v>Thomas2007OMD76</v>
@@ -4480,8 +4636,12 @@
         <f t="shared" si="11"/>
         <v>67.715000000000018</v>
       </c>
-    </row>
-    <row r="1048564" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="I189">
+        <f>(G189-G182)+I182</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1048564" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D1048564" s="1"/>
     </row>
   </sheetData>
@@ -4497,9 +4657,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D3643E-19A9-4BCA-984E-D3604CFC9FB7}">
   <dimension ref="A1:I200"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -4528,7 +4688,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -4557,7 +4717,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -4586,7 +4746,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -4615,7 +4775,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -4644,7 +4804,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -4673,7 +4833,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -4702,7 +4862,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -4731,7 +4891,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -4760,7 +4920,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -4789,7 +4949,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -4818,7 +4978,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -4847,7 +5007,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -4876,7 +5036,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -4905,7 +5065,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
@@ -4934,7 +5094,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -4963,7 +5123,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
@@ -4992,7 +5152,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
@@ -5021,7 +5181,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
@@ -5050,7 +5210,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>13</v>
       </c>
@@ -5079,7 +5239,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
@@ -5108,7 +5268,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
@@ -5137,7 +5297,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
@@ -5166,7 +5326,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>13</v>
       </c>
@@ -5195,7 +5355,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>13</v>
       </c>
@@ -5224,7 +5384,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>13</v>
       </c>
@@ -5253,7 +5413,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>13</v>
       </c>
@@ -5282,7 +5442,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -5311,7 +5471,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>13</v>
       </c>
@@ -5340,7 +5500,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>13</v>
       </c>
@@ -5369,7 +5529,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>13</v>
       </c>
@@ -5398,7 +5558,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>13</v>
       </c>
@@ -5427,7 +5587,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>13</v>
       </c>
@@ -5456,7 +5616,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>13</v>
       </c>
@@ -5485,7 +5645,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>13</v>
       </c>
@@ -5514,7 +5674,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>13</v>
       </c>
@@ -5543,7 +5703,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>13</v>
       </c>
@@ -5572,7 +5732,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>13</v>
       </c>
@@ -5601,7 +5761,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>13</v>
       </c>
@@ -5630,7 +5790,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
@@ -5659,7 +5819,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>13</v>
       </c>
@@ -5688,7 +5848,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>13</v>
       </c>
@@ -5717,7 +5877,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>13</v>
       </c>
@@ -5746,7 +5906,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>13</v>
       </c>
@@ -5775,7 +5935,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>13</v>
       </c>
@@ -5804,7 +5964,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
@@ -5833,7 +5993,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>13</v>
       </c>
@@ -5862,7 +6022,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -5875,7 +6035,7 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>14</v>
       </c>
@@ -5888,7 +6048,7 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>14</v>
       </c>
@@ -5901,7 +6061,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>14</v>
       </c>
@@ -5914,7 +6074,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>14</v>
       </c>
@@ -5943,7 +6103,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>14</v>
       </c>
@@ -5972,7 +6132,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>14</v>
       </c>
@@ -6001,7 +6161,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>14</v>
       </c>
@@ -6030,7 +6190,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -6059,7 +6219,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>14</v>
       </c>
@@ -6088,7 +6248,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>14</v>
       </c>
@@ -6117,7 +6277,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>14</v>
       </c>
@@ -6146,7 +6306,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>14</v>
       </c>
@@ -6175,7 +6335,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>14</v>
       </c>
@@ -6204,7 +6364,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>14</v>
       </c>
@@ -6233,7 +6393,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>14</v>
       </c>
@@ -6262,7 +6422,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>14</v>
       </c>
@@ -6291,7 +6451,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>14</v>
       </c>
@@ -6320,7 +6480,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>14</v>
       </c>
@@ -6349,7 +6509,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>14</v>
       </c>
@@ -6378,7 +6538,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>14</v>
       </c>
@@ -6407,7 +6567,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>14</v>
       </c>
@@ -6436,7 +6596,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>14</v>
       </c>
@@ -6465,7 +6625,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>14</v>
       </c>
@@ -6494,7 +6654,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>14</v>
       </c>
@@ -6523,7 +6683,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>14</v>
       </c>
@@ -6552,7 +6712,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -6581,7 +6741,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>14</v>
       </c>
@@ -6610,7 +6770,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>14</v>
       </c>
@@ -6639,7 +6799,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>14</v>
       </c>
@@ -6668,7 +6828,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>14</v>
       </c>
@@ -6697,7 +6857,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>14</v>
       </c>
@@ -6726,7 +6886,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>14</v>
       </c>
@@ -6755,7 +6915,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>14</v>
       </c>
@@ -6784,7 +6944,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -6813,7 +6973,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>14</v>
       </c>
@@ -6842,7 +7002,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>14</v>
       </c>
@@ -6871,7 +7031,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>14</v>
       </c>
@@ -6900,7 +7060,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>14</v>
       </c>
@@ -6929,7 +7089,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>14</v>
       </c>
@@ -6958,7 +7118,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>14</v>
       </c>
@@ -6987,7 +7147,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>14</v>
       </c>
@@ -7016,7 +7176,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>14</v>
       </c>
@@ -7045,7 +7205,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>14</v>
       </c>
@@ -7074,7 +7234,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>14</v>
       </c>
@@ -7103,7 +7263,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>14</v>
       </c>
@@ -7132,7 +7292,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>14</v>
       </c>
@@ -7161,7 +7321,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>14</v>
       </c>
@@ -7190,7 +7350,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>14</v>
       </c>
@@ -7219,7 +7379,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>14</v>
       </c>
@@ -7248,7 +7408,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>14</v>
       </c>
@@ -7277,7 +7437,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>15</v>
       </c>
@@ -7290,7 +7450,7 @@
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>15</v>
       </c>
@@ -7303,7 +7463,7 @@
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>15</v>
       </c>
@@ -7316,7 +7476,7 @@
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>15</v>
       </c>
@@ -7329,7 +7489,7 @@
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>15</v>
       </c>
@@ -7358,7 +7518,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>15</v>
       </c>
@@ -7387,7 +7547,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>15</v>
       </c>
@@ -7416,7 +7576,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>15</v>
       </c>
@@ -7445,7 +7605,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>15</v>
       </c>
@@ -7474,7 +7634,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>15</v>
       </c>
@@ -7503,7 +7663,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>15</v>
       </c>
@@ -7532,7 +7692,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>15</v>
       </c>
@@ -7561,7 +7721,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>15</v>
       </c>
@@ -7590,7 +7750,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>15</v>
       </c>
@@ -7619,7 +7779,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>15</v>
       </c>
@@ -7648,7 +7808,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>15</v>
       </c>
@@ -7677,7 +7837,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>15</v>
       </c>
@@ -7706,7 +7866,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>15</v>
       </c>
@@ -7735,7 +7895,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>15</v>
       </c>
@@ -7764,7 +7924,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>15</v>
       </c>
@@ -7793,7 +7953,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>15</v>
       </c>
@@ -7822,7 +7982,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>15</v>
       </c>
@@ -7851,7 +8011,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>15</v>
       </c>
@@ -7880,7 +8040,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>15</v>
       </c>
@@ -7909,7 +8069,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>15</v>
       </c>
@@ -7938,7 +8098,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>15</v>
       </c>
@@ -7967,7 +8127,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>15</v>
       </c>
@@ -7996,7 +8156,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>15</v>
       </c>
@@ -8025,7 +8185,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>15</v>
       </c>
@@ -8054,7 +8214,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>15</v>
       </c>
@@ -8083,7 +8243,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>15</v>
       </c>
@@ -8112,7 +8272,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>15</v>
       </c>
@@ -8141,7 +8301,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>15</v>
       </c>
@@ -8170,7 +8330,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>15</v>
       </c>
@@ -8199,7 +8359,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>15</v>
       </c>
@@ -8228,7 +8388,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>15</v>
       </c>
@@ -8257,7 +8417,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>15</v>
       </c>
@@ -8286,7 +8446,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>15</v>
       </c>
@@ -8315,7 +8475,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>15</v>
       </c>
@@ -8344,7 +8504,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>15</v>
       </c>
@@ -8373,7 +8533,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>15</v>
       </c>
@@ -8402,7 +8562,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>15</v>
       </c>
@@ -8431,7 +8591,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>15</v>
       </c>
@@ -8460,7 +8620,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>15</v>
       </c>
@@ -8489,7 +8649,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>15</v>
       </c>
@@ -8518,7 +8678,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>15</v>
       </c>
@@ -8547,7 +8707,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>15</v>
       </c>
@@ -8576,7 +8736,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>15</v>
       </c>
@@ -8605,7 +8765,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>15</v>
       </c>
@@ -8634,7 +8794,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>15</v>
       </c>
@@ -8663,7 +8823,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>15</v>
       </c>
@@ -8692,7 +8852,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>16</v>
       </c>
@@ -8705,7 +8865,7 @@
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>16</v>
       </c>
@@ -8718,7 +8878,7 @@
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>16</v>
       </c>
@@ -8731,7 +8891,7 @@
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>16</v>
       </c>
@@ -8744,7 +8904,7 @@
       <c r="H153" s="3"/>
       <c r="I153" s="3"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>16</v>
       </c>
@@ -8773,7 +8933,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>16</v>
       </c>
@@ -8802,7 +8962,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>16</v>
       </c>
@@ -8831,7 +8991,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>16</v>
       </c>
@@ -8860,7 +9020,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>16</v>
       </c>
@@ -8889,7 +9049,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>16</v>
       </c>
@@ -8918,7 +9078,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>16</v>
       </c>
@@ -8947,7 +9107,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>16</v>
       </c>
@@ -8976,7 +9136,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>16</v>
       </c>
@@ -9005,7 +9165,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>16</v>
       </c>
@@ -9034,7 +9194,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>16</v>
       </c>
@@ -9063,7 +9223,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>16</v>
       </c>
@@ -9092,7 +9252,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>16</v>
       </c>
@@ -9121,7 +9281,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>16</v>
       </c>
@@ -9150,7 +9310,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>16</v>
       </c>
@@ -9179,7 +9339,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>16</v>
       </c>
@@ -9208,7 +9368,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>16</v>
       </c>
@@ -9237,7 +9397,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>16</v>
       </c>
@@ -9266,7 +9426,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>16</v>
       </c>
@@ -9295,7 +9455,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>16</v>
       </c>
@@ -9324,7 +9484,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>16</v>
       </c>
@@ -9353,7 +9513,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>16</v>
       </c>
@@ -9382,7 +9542,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>16</v>
       </c>
@@ -9411,7 +9571,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>16</v>
       </c>
@@ -9440,7 +9600,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>16</v>
       </c>
@@ -9469,7 +9629,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>16</v>
       </c>
@@ -9498,7 +9658,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>16</v>
       </c>
@@ -9527,7 +9687,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>16</v>
       </c>
@@ -9556,7 +9716,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>16</v>
       </c>
@@ -9585,7 +9745,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>16</v>
       </c>
@@ -9614,7 +9774,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>16</v>
       </c>
@@ -9643,7 +9803,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>16</v>
       </c>
@@ -9672,7 +9832,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>16</v>
       </c>
@@ -9701,7 +9861,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>16</v>
       </c>
@@ -9730,7 +9890,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>16</v>
       </c>
@@ -9759,7 +9919,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>16</v>
       </c>
@@ -9788,7 +9948,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>16</v>
       </c>
@@ -9817,7 +9977,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>16</v>
       </c>
@@ -9846,7 +10006,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>16</v>
       </c>
@@ -9875,7 +10035,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>16</v>
       </c>
@@ -9904,7 +10064,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>16</v>
       </c>
@@ -9933,7 +10093,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>16</v>
       </c>
@@ -9962,7 +10122,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>16</v>
       </c>
@@ -9991,7 +10151,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>16</v>
       </c>
@@ -10020,7 +10180,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>16</v>
       </c>
@@ -10049,7 +10209,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>16</v>
       </c>
@@ -10078,7 +10238,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>16</v>
       </c>
@@ -10115,14 +10275,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42555D67-1672-42AA-A340-3C90B34A600E}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -10136,7 +10296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -10144,7 +10304,7 @@
         <v>281.10000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>45</v>
       </c>
@@ -10167,7 +10327,7 @@
         <v>10.600888888888887</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>75</v>
       </c>
@@ -10190,7 +10350,7 @@
         <v>9.4210666666666665</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>105</v>
       </c>
